--- a/VerveStacks_FRA/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CA8A1C5-1585-471E-8E24-EBAA569E8C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8447914-E8A4-4CAB-8371-8BF2C39F139E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{151710C7-CBEC-421D-8583-E82B54598B6D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9162E854-A696-4661-991A-4DC9D8D94C5B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2795,7 +2795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D00EF8D-7F68-436F-8D34-05A46F507160}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98FE4593-5E68-4AE8-B2AF-526A26894732}">
   <dimension ref="B9:T109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2874,19 +2874,19 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.27506149999999996</v>
+        <v>0.20014960000000001</v>
       </c>
       <c r="F11">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G11">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H11">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I11">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -2930,19 +2930,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.27506149999999996</v>
+        <v>0.20014960000000001</v>
       </c>
       <c r="F12">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G12">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H12">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I12">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J12" t="s">
         <v>23</v>
@@ -2986,19 +2986,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.27506149999999996</v>
+        <v>0.20014960000000001</v>
       </c>
       <c r="F13">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G13">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H13">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I13">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J13" t="s">
         <v>24</v>
@@ -3042,7 +3042,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.11272320000000002</v>
+        <v>9.0178560000000019E-2</v>
       </c>
       <c r="F14">
         <v>3583</v>
@@ -3098,7 +3098,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.46865000000000007</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -3154,7 +3154,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.46865000000000007</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -3210,7 +3210,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -3266,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -3322,7 +3322,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -3378,7 +3378,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -3434,7 +3434,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -3490,7 +3490,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -3546,7 +3546,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -3602,7 +3602,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -3658,7 +3658,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -3714,7 +3714,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3770,7 +3770,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3826,7 +3826,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.52272499999999988</v>
+        <v>0.41818</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -3882,7 +3882,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3938,7 +3938,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.49118125000000001</v>
+        <v>0.39294500000000004</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3994,7 +3994,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -4050,7 +4050,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.54075000000000006</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -4106,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.54075000000000006</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -4162,7 +4162,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.23883125000000002</v>
+        <v>0.19106500000000001</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4218,7 +4218,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -4274,7 +4274,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -4330,7 +4330,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -4386,7 +4386,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000006</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -4442,7 +4442,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.19827499999999998</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -4498,7 +4498,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.19827499999999998</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -4554,7 +4554,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.18025000000000002</v>
+        <v>0.14420000000000002</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -4610,7 +4610,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -4666,7 +4666,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -4722,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -4778,7 +4778,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.22981874999999999</v>
+        <v>0.18385500000000005</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4834,7 +4834,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.22981874999999999</v>
+        <v>0.18385500000000005</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4890,7 +4890,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999996</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4946,7 +4946,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -5002,7 +5002,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999996</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5058,7 +5058,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5114,7 +5114,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.22981874999999999</v>
+        <v>0.18385500000000005</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -5170,7 +5170,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -5226,7 +5226,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -5282,7 +5282,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -5338,7 +5338,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -5394,7 +5394,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -5450,7 +5450,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -5506,7 +5506,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -5562,7 +5562,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999996</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -5618,7 +5618,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.22981874999999999</v>
+        <v>0.18385500000000005</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -5674,7 +5674,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.19827500000000001</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -5730,7 +5730,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.31994374999999997</v>
+        <v>0.25595499999999999</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -5786,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.31994374999999997</v>
+        <v>0.25595499999999999</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -5842,7 +5842,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -5898,7 +5898,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -5954,7 +5954,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -6010,7 +6010,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6066,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -6122,7 +6122,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.30191875000000001</v>
+        <v>0.241535</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6178,7 +6178,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.30191875000000001</v>
+        <v>0.241535</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -6234,7 +6234,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -6290,7 +6290,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.28839999999999999</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -6346,7 +6346,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.30191875000000001</v>
+        <v>0.241535</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -6402,7 +6402,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.30191875000000001</v>
+        <v>0.241535</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -6458,7 +6458,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.28839999999999999</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -6514,7 +6514,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.29741250000000002</v>
+        <v>0.23793000000000003</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -6570,7 +6570,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.43259999999999998</v>
+        <v>0.34608000000000005</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -6626,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -6682,7 +6682,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6738,7 +6738,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6794,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.450625</v>
+        <v>0.36050000000000004</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6850,7 +6850,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6906,7 +6906,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.22981874999999999</v>
+        <v>0.18385499999999999</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -6962,7 +6962,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7018,7 +7018,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.24333750000000001</v>
+        <v>0.19466999999999998</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7074,7 +7074,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7130,7 +7130,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.24333750000000001</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7186,7 +7186,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.22080625000000001</v>
+        <v>0.17664500000000005</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7242,7 +7242,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.22080625000000001</v>
+        <v>0.176645</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7298,7 +7298,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.22080625000000001</v>
+        <v>0.176645</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7354,7 +7354,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.21629999999999999</v>
+        <v>0.17304000000000003</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7410,7 +7410,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.19827500000000001</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7466,7 +7466,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.21629999999999999</v>
+        <v>0.17304000000000003</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -7522,7 +7522,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.22981874999999999</v>
+        <v>0.18385500000000005</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -7578,7 +7578,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.19827500000000001</v>
+        <v>0.15862000000000001</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -7634,7 +7634,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.24333750000000001</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7690,7 +7690,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.24333750000000001</v>
+        <v>0.19467000000000001</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7746,7 +7746,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.28389375</v>
+        <v>0.22711500000000001</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7802,7 +7802,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.31543749999999998</v>
+        <v>0.25235000000000002</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7858,7 +7858,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.28389375</v>
+        <v>0.22711500000000001</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7914,7 +7914,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.27938750000000001</v>
+        <v>0.22351000000000007</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -7970,7 +7970,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.27938750000000001</v>
+        <v>0.22351000000000007</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8026,7 +8026,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8082,7 +8082,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.27037500000000003</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8138,7 +8138,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.29290625000000003</v>
+        <v>0.23432500000000003</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8194,7 +8194,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8250,7 +8250,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8306,7 +8306,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.26136249999999994</v>
+        <v>0.20909</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8362,7 +8362,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8413,7 +8413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{333DC0A8-F1F0-4958-916F-9C0916E0D7A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21869119-A803-4522-86C5-AB4EEE3C66A7}">
   <dimension ref="B9:T347"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8498,7 +8498,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G11">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -8551,7 +8551,7 @@
         <v>0.06</v>
       </c>
       <c r="G12">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -8604,7 +8604,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G13">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -8657,7 +8657,7 @@
         <v>1.9420000000000002</v>
       </c>
       <c r="G14">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H14">
         <v>3850.0000000000005</v>
@@ -8710,7 +8710,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G15">
-        <v>0.29869999999999997</v>
+        <v>0.23896000000000001</v>
       </c>
       <c r="H15">
         <v>4427.5</v>
@@ -8763,7 +8763,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G16">
-        <v>0.23690000000000003</v>
+        <v>0.18952000000000002</v>
       </c>
       <c r="H16">
         <v>4427.5</v>
@@ -8816,7 +8816,7 @@
         <v>0.05</v>
       </c>
       <c r="G17">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H17">
         <v>5197.5</v>
@@ -8869,7 +8869,7 @@
         <v>0.15</v>
       </c>
       <c r="G18">
-        <v>0.27295000000000003</v>
+        <v>0.21836000000000003</v>
       </c>
       <c r="H18">
         <v>4427.5</v>
@@ -8922,7 +8922,7 @@
         <v>0.60299999999999976</v>
       </c>
       <c r="G19">
-        <v>0.37080000000000002</v>
+        <v>0.29664000000000001</v>
       </c>
       <c r="H19">
         <v>2200</v>
@@ -8975,7 +8975,7 @@
         <v>0.63</v>
       </c>
       <c r="G20">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H20">
         <v>2200</v>
@@ -9028,7 +9028,7 @@
         <v>0.63</v>
       </c>
       <c r="G21">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H21">
         <v>2200</v>
@@ -9081,7 +9081,7 @@
         <v>0.64700000000000002</v>
       </c>
       <c r="G22">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H22">
         <v>2200</v>
@@ -9134,7 +9134,7 @@
         <v>8.3752999999999993</v>
       </c>
       <c r="G23">
-        <v>0.61799999999999999</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H23">
         <v>1100</v>
@@ -9187,7 +9187,7 @@
         <v>0.12</v>
       </c>
       <c r="G24">
-        <v>0.53560000000000008</v>
+        <v>0.42848000000000008</v>
       </c>
       <c r="H24">
         <v>1265</v>
@@ -9240,7 +9240,7 @@
         <v>0.12</v>
       </c>
       <c r="G25">
-        <v>0.53560000000000008</v>
+        <v>0.42848000000000008</v>
       </c>
       <c r="H25">
         <v>1265</v>
@@ -9293,7 +9293,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="G26">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H26">
         <v>1100</v>
@@ -9346,7 +9346,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="G27">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H27">
         <v>1100</v>
@@ -9399,7 +9399,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="G28">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -9452,7 +9452,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="G29">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -9505,7 +9505,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G30">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -9558,7 +9558,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="G31">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -9611,7 +9611,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G32">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -9664,7 +9664,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G33">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H33">
         <v>1100</v>
@@ -9717,7 +9717,7 @@
         <v>0.44</v>
       </c>
       <c r="G34">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H34">
         <v>1100</v>
@@ -9770,7 +9770,7 @@
         <v>0.44</v>
       </c>
       <c r="G35">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H35">
         <v>1100</v>
@@ -9823,7 +9823,7 @@
         <v>0.499</v>
       </c>
       <c r="G36">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H36">
         <v>1100</v>
@@ -9876,7 +9876,7 @@
         <v>0.499</v>
       </c>
       <c r="G37">
-        <v>0.59739999999999993</v>
+        <v>0.47791999999999996</v>
       </c>
       <c r="H37">
         <v>1100</v>
@@ -9929,7 +9929,7 @@
         <v>0.435</v>
       </c>
       <c r="G38">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H38">
         <v>1100</v>
@@ -9982,7 +9982,7 @@
         <v>0.45</v>
       </c>
       <c r="G39">
-        <v>0.56135000000000002</v>
+        <v>0.44908000000000003</v>
       </c>
       <c r="H39">
         <v>1100</v>
@@ -10035,7 +10035,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G40">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H40">
         <v>1265</v>
@@ -10088,7 +10088,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="G41">
-        <v>0.61799999999999999</v>
+        <v>0.49440000000000001</v>
       </c>
       <c r="H41">
         <v>1100</v>
@@ -10141,7 +10141,7 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="G42">
-        <v>0.27295000000000003</v>
+        <v>0.21836</v>
       </c>
       <c r="H42">
         <v>1012</v>
@@ -10194,7 +10194,7 @@
         <v>0.125</v>
       </c>
       <c r="G43">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H43">
         <v>1012</v>
@@ -10247,7 +10247,7 @@
         <v>0.2</v>
       </c>
       <c r="G44">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H44">
         <v>1012</v>
@@ -10300,7 +10300,7 @@
         <v>0.2</v>
       </c>
       <c r="G45">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H45">
         <v>1012</v>
@@ -10353,7 +10353,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G46">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000006</v>
       </c>
       <c r="H46">
         <v>1188</v>
@@ -10406,7 +10406,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G47">
-        <v>0.22659999999999997</v>
+        <v>0.18128</v>
       </c>
       <c r="H47">
         <v>1188</v>
@@ -10459,7 +10459,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G48">
-        <v>0.22659999999999997</v>
+        <v>0.18128</v>
       </c>
       <c r="H48">
         <v>1188</v>
@@ -10512,7 +10512,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G49">
-        <v>0.20600000000000002</v>
+        <v>0.16480000000000003</v>
       </c>
       <c r="H49">
         <v>1188</v>
@@ -10565,7 +10565,7 @@
         <v>0.02</v>
       </c>
       <c r="G50">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H50">
         <v>1188</v>
@@ -10618,7 +10618,7 @@
         <v>0.128</v>
       </c>
       <c r="G51">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H51">
         <v>1012</v>
@@ -10671,7 +10671,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G52">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H52">
         <v>1188</v>
@@ -10724,7 +10724,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G53">
-        <v>0.26264999999999999</v>
+        <v>0.21012000000000003</v>
       </c>
       <c r="H53">
         <v>1188</v>
@@ -10777,7 +10777,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G54">
-        <v>0.26264999999999999</v>
+        <v>0.21012000000000003</v>
       </c>
       <c r="H54">
         <v>1188</v>
@@ -10830,7 +10830,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G55">
-        <v>0.26264999999999999</v>
+        <v>0.21011999999999997</v>
       </c>
       <c r="H55">
         <v>1188</v>
@@ -10883,7 +10883,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G56">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H56">
         <v>1188</v>
@@ -10936,7 +10936,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.26264999999999999</v>
+        <v>0.21011999999999997</v>
       </c>
       <c r="H57">
         <v>1188</v>
@@ -10989,7 +10989,7 @@
         <v>0.03</v>
       </c>
       <c r="G58">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H58">
         <v>1188</v>
@@ -11042,7 +11042,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G59">
-        <v>0.26264999999999999</v>
+        <v>0.21012000000000003</v>
       </c>
       <c r="H59">
         <v>1188</v>
@@ -11095,7 +11095,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G60">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H60">
         <v>1188</v>
@@ -11148,7 +11148,7 @@
         <v>0.04</v>
       </c>
       <c r="G61">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H61">
         <v>1188</v>
@@ -11201,7 +11201,7 @@
         <v>0.04</v>
       </c>
       <c r="G62">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H62">
         <v>1188</v>
@@ -11254,7 +11254,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G63">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H63">
         <v>1188</v>
@@ -11307,7 +11307,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G64">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H64">
         <v>1188</v>
@@ -11360,7 +11360,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G65">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H65">
         <v>1188</v>
@@ -11413,7 +11413,7 @@
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="G66">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H66">
         <v>1188</v>
@@ -11466,7 +11466,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G67">
-        <v>0.26264999999999999</v>
+        <v>0.21011999999999997</v>
       </c>
       <c r="H67">
         <v>1188</v>
@@ -11519,7 +11519,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G68">
-        <v>0.26264999999999999</v>
+        <v>0.21012000000000003</v>
       </c>
       <c r="H68">
         <v>1188</v>
@@ -11572,7 +11572,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G69">
-        <v>0.2266</v>
+        <v>0.18128</v>
       </c>
       <c r="H69">
         <v>1188</v>
@@ -11625,7 +11625,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G70">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H70">
         <v>1633.5000000000002</v>
@@ -11678,7 +11678,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G71">
-        <v>0.36564999999999998</v>
+        <v>0.29252</v>
       </c>
       <c r="H71">
         <v>1633.5000000000002</v>
@@ -11731,7 +11731,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G72">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H72">
         <v>1782.0000000000002</v>
@@ -11784,7 +11784,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G73">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H73">
         <v>1782.0000000000002</v>
@@ -11837,7 +11837,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G74">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H74">
         <v>1782.0000000000002</v>
@@ -11890,7 +11890,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G75">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H75">
         <v>1782.0000000000002</v>
@@ -11943,7 +11943,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G76">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H76">
         <v>1782.0000000000002</v>
@@ -11996,7 +11996,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G77">
-        <v>0.34505000000000002</v>
+        <v>0.27604000000000001</v>
       </c>
       <c r="H77">
         <v>1782.0000000000002</v>
@@ -12049,7 +12049,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G78">
-        <v>0.34505000000000002</v>
+        <v>0.27604000000000001</v>
       </c>
       <c r="H78">
         <v>1782.0000000000002</v>
@@ -12102,7 +12102,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G79">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H79">
         <v>1518.0000000000002</v>
@@ -12155,7 +12155,7 @@
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="G80">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H80">
         <v>1782.0000000000002</v>
@@ -12208,7 +12208,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G81">
-        <v>0.34505000000000002</v>
+        <v>0.27604000000000001</v>
       </c>
       <c r="H81">
         <v>1782.0000000000002</v>
@@ -12261,7 +12261,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G82">
-        <v>0.34505000000000002</v>
+        <v>0.27604000000000001</v>
       </c>
       <c r="H82">
         <v>1782.0000000000002</v>
@@ -12314,7 +12314,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="G83">
-        <v>0.3296</v>
+        <v>0.26368000000000003</v>
       </c>
       <c r="H83">
         <v>1782.0000000000002</v>
@@ -12367,7 +12367,7 @@
         <v>4.87E-2</v>
       </c>
       <c r="G84">
-        <v>0.33990000000000004</v>
+        <v>0.27192000000000005</v>
       </c>
       <c r="H84">
         <v>1782.0000000000005</v>
@@ -21430,7 +21430,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G255">
-        <v>0.49440000000000001</v>
+        <v>0.39552000000000004</v>
       </c>
       <c r="H255">
         <v>1633.5000000000002</v>
@@ -21483,7 +21483,7 @@
         <v>0.2</v>
       </c>
       <c r="G256">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H256">
         <v>1391.5</v>
@@ -21536,7 +21536,7 @@
         <v>0.2</v>
       </c>
       <c r="G257">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H257">
         <v>1391.5</v>
@@ -21589,7 +21589,7 @@
         <v>0.2</v>
       </c>
       <c r="G258">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H258">
         <v>1391.5</v>
@@ -21642,7 +21642,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G259">
-        <v>0.51500000000000001</v>
+        <v>0.41200000000000003</v>
       </c>
       <c r="H259">
         <v>1391.5</v>
@@ -21695,7 +21695,7 @@
         <v>0.125</v>
       </c>
       <c r="G260">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H260">
         <v>1138.5</v>
@@ -21748,7 +21748,7 @@
         <v>0.125</v>
       </c>
       <c r="G261">
-        <v>0.26264999999999999</v>
+        <v>0.21012</v>
       </c>
       <c r="H261">
         <v>1138.5</v>
@@ -21801,7 +21801,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G262">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H262">
         <v>1336.5</v>
@@ -21854,7 +21854,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G263">
-        <v>0.27810000000000001</v>
+        <v>0.22247999999999998</v>
       </c>
       <c r="H263">
         <v>1336.5</v>
@@ -21907,7 +21907,7 @@
         <v>0.05</v>
       </c>
       <c r="G264">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H264">
         <v>1336.5</v>
@@ -21960,7 +21960,7 @@
         <v>0.04</v>
       </c>
       <c r="G265">
-        <v>0.27810000000000001</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H265">
         <v>1336.5</v>
@@ -22013,7 +22013,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G266">
-        <v>0.25235000000000002</v>
+        <v>0.20188000000000003</v>
       </c>
       <c r="H266">
         <v>1336.5</v>
@@ -22066,7 +22066,7 @@
         <v>0.02</v>
       </c>
       <c r="G267">
-        <v>0.25235000000000002</v>
+        <v>0.20188</v>
       </c>
       <c r="H267">
         <v>1336.5</v>
@@ -22119,7 +22119,7 @@
         <v>0.02</v>
       </c>
       <c r="G268">
-        <v>0.25235000000000002</v>
+        <v>0.20188</v>
       </c>
       <c r="H268">
         <v>1336.5</v>
@@ -22172,7 +22172,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G269">
-        <v>0.2472</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="H269">
         <v>1138.5</v>
@@ -22225,7 +22225,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G270">
-        <v>0.2266</v>
+        <v>0.18128</v>
       </c>
       <c r="H270">
         <v>1138.5</v>
@@ -22278,7 +22278,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G271">
-        <v>0.24719999999999998</v>
+        <v>0.19776000000000002</v>
       </c>
       <c r="H271">
         <v>1138.5</v>
@@ -22331,7 +22331,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G272">
-        <v>0.26264999999999999</v>
+        <v>0.21012000000000003</v>
       </c>
       <c r="H272">
         <v>1138.5</v>
@@ -22384,7 +22384,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G273">
-        <v>0.2266</v>
+        <v>0.18128</v>
       </c>
       <c r="H273">
         <v>1138.5</v>
@@ -22437,7 +22437,7 @@
         <v>0.04</v>
       </c>
       <c r="G274">
-        <v>0.27810000000000001</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H274">
         <v>1336.5</v>
@@ -22490,7 +22490,7 @@
         <v>0.04</v>
       </c>
       <c r="G275">
-        <v>0.27810000000000001</v>
+        <v>0.22248000000000001</v>
       </c>
       <c r="H275">
         <v>1336.5</v>
@@ -22543,7 +22543,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G276">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="H276">
         <v>1265</v>
@@ -22596,7 +22596,7 @@
         <v>0.126</v>
       </c>
       <c r="G277">
-        <v>0.36049999999999999</v>
+        <v>0.28839999999999999</v>
       </c>
       <c r="H277">
         <v>1265</v>
@@ -22649,7 +22649,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G278">
-        <v>0.32445000000000002</v>
+        <v>0.25956000000000001</v>
       </c>
       <c r="H278">
         <v>1485.0000000000002</v>
@@ -22702,7 +22702,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G279">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H279">
         <v>1930.5000000000002</v>
@@ -22755,7 +22755,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G280">
-        <v>0.31930000000000003</v>
+        <v>0.25544000000000006</v>
       </c>
       <c r="H280">
         <v>1930.5000000000002</v>
@@ -22808,7 +22808,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G281">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H281">
         <v>1930.5000000000002</v>
@@ -22861,7 +22861,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G282">
-        <v>0.309</v>
+        <v>0.2472</v>
       </c>
       <c r="H282">
         <v>1930.5000000000005</v>
@@ -22914,7 +22914,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G283">
-        <v>0.33475000000000005</v>
+        <v>0.26780000000000004</v>
       </c>
       <c r="H283">
         <v>1930.5000000000007</v>
@@ -22967,7 +22967,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G284">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H284">
         <v>1930.5000000000007</v>
@@ -23020,7 +23020,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G285">
-        <v>0.29869999999999997</v>
+        <v>0.23896000000000001</v>
       </c>
       <c r="H285">
         <v>1930.5000000000005</v>
@@ -23073,7 +23073,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G286">
-        <v>0.29869999999999997</v>
+        <v>0.23895999999999998</v>
       </c>
       <c r="H286">
         <v>1930.5000000000002</v>
@@ -23126,7 +23126,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G287">
-        <v>0.28840000000000005</v>
+        <v>0.23072000000000004</v>
       </c>
       <c r="H287">
         <v>1930.5000000000007</v>
@@ -23194,7 +23194,7 @@
         <v>33</v>
       </c>
       <c r="L288">
-        <v>0.18536586510950334</v>
+        <v>0.1853658651095034</v>
       </c>
       <c r="N288" t="s">
         <v>314</v>

--- a/VerveStacks_FRA/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8447914-E8A4-4CAB-8371-8BF2C39F139E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80FD8B40-23AF-4431-99EC-0F773728BE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9162E854-A696-4661-991A-4DC9D8D94C5B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6F8BB7FB-25B9-416E-9171-F2EEB0925DF7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2795,7 +2795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98FE4593-5E68-4AE8-B2AF-526A26894732}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C001207A-2CFF-423C-993E-644480D17306}">
   <dimension ref="B9:T109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2874,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.20014960000000001</v>
+        <v>0.20515333999999999</v>
       </c>
       <c r="F11">
         <v>2445</v>
@@ -2930,7 +2930,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.20014960000000001</v>
+        <v>0.20515333999999999</v>
       </c>
       <c r="F12">
         <v>2445</v>
@@ -2986,7 +2986,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.20014960000000001</v>
+        <v>0.20515333999999999</v>
       </c>
       <c r="F13">
         <v>2445</v>
@@ -3042,7 +3042,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>9.0178560000000019E-2</v>
+        <v>9.2433024000000016E-2</v>
       </c>
       <c r="F14">
         <v>3583</v>
@@ -3098,7 +3098,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.37492000000000003</v>
+        <v>0.38429300000000005</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -3154,7 +3154,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.37492000000000003</v>
+        <v>0.38429300000000005</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -3210,7 +3210,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.41818</v>
+        <v>0.42863449999999986</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -3266,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.41818</v>
+        <v>0.42863449999999992</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -3322,7 +3322,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.41818</v>
+        <v>0.42863449999999992</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -3378,7 +3378,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -3434,7 +3434,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.41818</v>
+        <v>0.42863449999999992</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -3490,7 +3490,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -3546,7 +3546,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -3602,7 +3602,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -3658,7 +3658,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -3714,7 +3714,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3770,7 +3770,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.41818</v>
+        <v>0.42863449999999992</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3826,7 +3826,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.41818</v>
+        <v>0.42863449999999992</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -3882,7 +3882,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3938,7 +3938,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.39294500000000004</v>
+        <v>0.40276862499999999</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3994,7 +3994,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.36050000000000004</v>
+        <v>0.36951250000000002</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -4050,7 +4050,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.43259999999999998</v>
+        <v>0.44341499999999995</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -4106,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.43259999999999998</v>
+        <v>0.44341499999999995</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -4162,7 +4162,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.19106500000000001</v>
+        <v>0.19584162500000005</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4218,7 +4218,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.20909</v>
+        <v>0.21431724999999996</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -4274,7 +4274,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.20909</v>
+        <v>0.21431724999999993</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -4330,7 +4330,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.20909</v>
+        <v>0.21431724999999993</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -4386,7 +4386,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.20188000000000006</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -4442,7 +4442,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.15862000000000001</v>
+        <v>0.16258549999999999</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -4498,7 +4498,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.15862000000000001</v>
+        <v>0.16258549999999999</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -4554,7 +4554,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.14420000000000002</v>
+        <v>0.14780500000000002</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -4610,7 +4610,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -4666,7 +4666,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.20909</v>
+        <v>0.21431724999999996</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -4722,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -4778,7 +4778,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.18385500000000005</v>
+        <v>0.188451375</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4834,7 +4834,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.18385500000000005</v>
+        <v>0.188451375</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4890,7 +4890,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.18385499999999996</v>
+        <v>0.18845137499999998</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4946,7 +4946,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -5002,7 +5002,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.18385499999999996</v>
+        <v>0.18845137499999998</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -5058,7 +5058,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.18385499999999999</v>
+        <v>0.188451375</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -5114,7 +5114,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.18385500000000005</v>
+        <v>0.188451375</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -5170,7 +5170,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000006</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -5226,7 +5226,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -5282,7 +5282,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -5338,7 +5338,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -5394,7 +5394,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -5450,7 +5450,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000006</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -5506,7 +5506,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -5562,7 +5562,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.18385499999999996</v>
+        <v>0.188451375</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -5618,7 +5618,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.18385500000000005</v>
+        <v>0.188451375</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -5674,7 +5674,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.15862000000000001</v>
+        <v>0.16258549999999999</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -5730,7 +5730,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.25595499999999999</v>
+        <v>0.26235387499999996</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -5786,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.25595499999999999</v>
+        <v>0.26235387499999996</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -5842,7 +5842,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.23793000000000003</v>
+        <v>0.24387825000000002</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -5898,7 +5898,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.23793000000000003</v>
+        <v>0.24387825000000002</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -5954,7 +5954,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.23793000000000003</v>
+        <v>0.24387825000000002</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -6010,7 +6010,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -6066,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -6122,7 +6122,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.241535</v>
+        <v>0.24757337499999998</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6178,7 +6178,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.241535</v>
+        <v>0.24757337499999998</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -6234,7 +6234,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.23793000000000003</v>
+        <v>0.24387825000000002</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -6290,7 +6290,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.23072000000000004</v>
+        <v>0.236488</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -6346,7 +6346,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.241535</v>
+        <v>0.24757337499999998</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -6402,7 +6402,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.241535</v>
+        <v>0.24757337499999998</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -6458,7 +6458,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.23072000000000004</v>
+        <v>0.236488</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -6514,7 +6514,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.23793000000000003</v>
+        <v>0.24387825000000002</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -6570,7 +6570,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.34608000000000005</v>
+        <v>0.35473199999999999</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -6626,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.36050000000000004</v>
+        <v>0.36951250000000008</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -6682,7 +6682,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.36050000000000004</v>
+        <v>0.36951250000000008</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6738,7 +6738,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.36050000000000004</v>
+        <v>0.36951250000000008</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6794,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.36050000000000004</v>
+        <v>0.36951250000000002</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6850,7 +6850,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6906,7 +6906,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.18385499999999999</v>
+        <v>0.188451375</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -6962,7 +6962,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.20909</v>
+        <v>0.21431724999999996</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -7018,7 +7018,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.19466999999999998</v>
+        <v>0.19953675000000001</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -7074,7 +7074,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.20909</v>
+        <v>0.21431724999999993</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -7130,7 +7130,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.19467000000000001</v>
+        <v>0.19953675000000001</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7186,7 +7186,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.17664500000000005</v>
+        <v>0.18106112499999999</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7242,7 +7242,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.176645</v>
+        <v>0.18106112499999999</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7298,7 +7298,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.176645</v>
+        <v>0.18106112499999999</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7354,7 +7354,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.17304000000000003</v>
+        <v>0.177366</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7410,7 +7410,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.15862000000000001</v>
+        <v>0.16258549999999997</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7466,7 +7466,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.17304000000000003</v>
+        <v>0.177366</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -7522,7 +7522,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.18385500000000005</v>
+        <v>0.188451375</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -7578,7 +7578,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.15862000000000001</v>
+        <v>0.16258549999999997</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -7634,7 +7634,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.19467000000000001</v>
+        <v>0.19953675000000001</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7690,7 +7690,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.19467000000000001</v>
+        <v>0.19953675000000001</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7746,7 +7746,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.22711500000000001</v>
+        <v>0.23279287499999998</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7802,7 +7802,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.25235000000000002</v>
+        <v>0.25865874999999999</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7858,7 +7858,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.22711500000000001</v>
+        <v>0.23279287499999998</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7914,7 +7914,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.22351000000000007</v>
+        <v>0.22909774999999999</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -7970,7 +7970,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.22351000000000007</v>
+        <v>0.22909774999999999</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -8026,7 +8026,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.20909</v>
+        <v>0.21431724999999996</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -8082,7 +8082,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.21629999999999999</v>
+        <v>0.22170749999999997</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -8138,7 +8138,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.23432500000000003</v>
+        <v>0.24018312500000005</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8194,7 +8194,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8250,7 +8250,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.20909</v>
+        <v>0.21431725000000001</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8306,7 +8306,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.20909</v>
+        <v>0.21431724999999996</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8362,7 +8362,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.20188000000000003</v>
+        <v>0.20692700000000003</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8413,7 +8413,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21869119-A803-4522-86C5-AB4EEE3C66A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B332FF1C-55AE-4261-A54B-6607DEB92DDF}">
   <dimension ref="B9:T347"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8498,7 +8498,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G11">
-        <v>0.21012</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -8551,7 +8551,7 @@
         <v>0.06</v>
       </c>
       <c r="G12">
-        <v>0.26368000000000003</v>
+        <v>0.27027200000000001</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -8604,7 +8604,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G13">
-        <v>0.26368000000000003</v>
+        <v>0.27027200000000001</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -8657,7 +8657,7 @@
         <v>1.9420000000000002</v>
       </c>
       <c r="G14">
-        <v>0.28839999999999999</v>
+        <v>0.29560999999999993</v>
       </c>
       <c r="H14">
         <v>3850.0000000000005</v>
@@ -8710,7 +8710,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G15">
-        <v>0.23896000000000001</v>
+        <v>0.24493399999999996</v>
       </c>
       <c r="H15">
         <v>4427.5</v>
@@ -8763,7 +8763,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G16">
-        <v>0.18952000000000002</v>
+        <v>0.19425800000000001</v>
       </c>
       <c r="H16">
         <v>4427.5</v>
@@ -8816,7 +8816,7 @@
         <v>0.05</v>
       </c>
       <c r="G17">
-        <v>0.23072000000000004</v>
+        <v>0.236488</v>
       </c>
       <c r="H17">
         <v>5197.5</v>
@@ -8869,7 +8869,7 @@
         <v>0.15</v>
       </c>
       <c r="G18">
-        <v>0.21836000000000003</v>
+        <v>0.22381900000000002</v>
       </c>
       <c r="H18">
         <v>4427.5</v>
@@ -8922,7 +8922,7 @@
         <v>0.60299999999999976</v>
       </c>
       <c r="G19">
-        <v>0.29664000000000001</v>
+        <v>0.30405599999999999</v>
       </c>
       <c r="H19">
         <v>2200</v>
@@ -8975,7 +8975,7 @@
         <v>0.63</v>
       </c>
       <c r="G20">
-        <v>0.28839999999999999</v>
+        <v>0.29560999999999998</v>
       </c>
       <c r="H20">
         <v>2200</v>
@@ -9028,7 +9028,7 @@
         <v>0.63</v>
       </c>
       <c r="G21">
-        <v>0.28839999999999999</v>
+        <v>0.29560999999999998</v>
       </c>
       <c r="H21">
         <v>2200</v>
@@ -9081,7 +9081,7 @@
         <v>0.64700000000000002</v>
       </c>
       <c r="G22">
-        <v>0.28839999999999999</v>
+        <v>0.29560999999999998</v>
       </c>
       <c r="H22">
         <v>2200</v>
@@ -9134,7 +9134,7 @@
         <v>8.3752999999999993</v>
       </c>
       <c r="G23">
-        <v>0.49440000000000001</v>
+        <v>0.50675999999999999</v>
       </c>
       <c r="H23">
         <v>1100</v>
@@ -9187,7 +9187,7 @@
         <v>0.12</v>
       </c>
       <c r="G24">
-        <v>0.42848000000000008</v>
+        <v>0.43919200000000003</v>
       </c>
       <c r="H24">
         <v>1265</v>
@@ -9240,7 +9240,7 @@
         <v>0.12</v>
       </c>
       <c r="G25">
-        <v>0.42848000000000008</v>
+        <v>0.43919200000000003</v>
       </c>
       <c r="H25">
         <v>1265</v>
@@ -9293,7 +9293,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="G26">
-        <v>0.47791999999999996</v>
+        <v>0.48986799999999986</v>
       </c>
       <c r="H26">
         <v>1100</v>
@@ -9346,7 +9346,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="G27">
-        <v>0.47791999999999996</v>
+        <v>0.48986799999999991</v>
       </c>
       <c r="H27">
         <v>1100</v>
@@ -9399,7 +9399,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="G28">
-        <v>0.47791999999999996</v>
+        <v>0.48986799999999991</v>
       </c>
       <c r="H28">
         <v>1100</v>
@@ -9452,7 +9452,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="G29">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H29">
         <v>1100</v>
@@ -9505,7 +9505,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="G30">
-        <v>0.47791999999999996</v>
+        <v>0.48986799999999991</v>
       </c>
       <c r="H30">
         <v>1100</v>
@@ -9558,7 +9558,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="G31">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H31">
         <v>1100</v>
@@ -9611,7 +9611,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G32">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H32">
         <v>1100</v>
@@ -9664,7 +9664,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G33">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H33">
         <v>1100</v>
@@ -9717,7 +9717,7 @@
         <v>0.44</v>
       </c>
       <c r="G34">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H34">
         <v>1100</v>
@@ -9770,7 +9770,7 @@
         <v>0.44</v>
       </c>
       <c r="G35">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H35">
         <v>1100</v>
@@ -9823,7 +9823,7 @@
         <v>0.499</v>
       </c>
       <c r="G36">
-        <v>0.47791999999999996</v>
+        <v>0.48986799999999991</v>
       </c>
       <c r="H36">
         <v>1100</v>
@@ -9876,7 +9876,7 @@
         <v>0.499</v>
       </c>
       <c r="G37">
-        <v>0.47791999999999996</v>
+        <v>0.48986799999999991</v>
       </c>
       <c r="H37">
         <v>1100</v>
@@ -9929,7 +9929,7 @@
         <v>0.435</v>
       </c>
       <c r="G38">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H38">
         <v>1100</v>
@@ -9982,7 +9982,7 @@
         <v>0.45</v>
       </c>
       <c r="G39">
-        <v>0.44908000000000003</v>
+        <v>0.46030699999999997</v>
       </c>
       <c r="H39">
         <v>1100</v>
@@ -10035,7 +10035,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G40">
-        <v>0.41200000000000003</v>
+        <v>0.42230000000000001</v>
       </c>
       <c r="H40">
         <v>1265</v>
@@ -10088,7 +10088,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="G41">
-        <v>0.49440000000000001</v>
+        <v>0.50675999999999999</v>
       </c>
       <c r="H41">
         <v>1100</v>
@@ -10141,7 +10141,7 @@
         <v>0.20300000000000001</v>
       </c>
       <c r="G42">
-        <v>0.21836</v>
+        <v>0.22381900000000005</v>
       </c>
       <c r="H42">
         <v>1012</v>
@@ -10194,7 +10194,7 @@
         <v>0.125</v>
       </c>
       <c r="G43">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999996</v>
       </c>
       <c r="H43">
         <v>1012</v>
@@ -10247,7 +10247,7 @@
         <v>0.2</v>
       </c>
       <c r="G44">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999993</v>
       </c>
       <c r="H44">
         <v>1012</v>
@@ -10300,7 +10300,7 @@
         <v>0.2</v>
       </c>
       <c r="G45">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999993</v>
       </c>
       <c r="H45">
         <v>1012</v>
@@ -10353,7 +10353,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G46">
-        <v>0.23072000000000006</v>
+        <v>0.23648800000000003</v>
       </c>
       <c r="H46">
         <v>1188</v>
@@ -10406,7 +10406,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G47">
-        <v>0.18128</v>
+        <v>0.18581199999999998</v>
       </c>
       <c r="H47">
         <v>1188</v>
@@ -10459,7 +10459,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G48">
-        <v>0.18128</v>
+        <v>0.18581199999999998</v>
       </c>
       <c r="H48">
         <v>1188</v>
@@ -10512,7 +10512,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="G49">
-        <v>0.16480000000000003</v>
+        <v>0.16892000000000001</v>
       </c>
       <c r="H49">
         <v>1188</v>
@@ -10565,7 +10565,7 @@
         <v>0.02</v>
       </c>
       <c r="G50">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000003</v>
       </c>
       <c r="H50">
         <v>1188</v>
@@ -10618,7 +10618,7 @@
         <v>0.128</v>
       </c>
       <c r="G51">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999996</v>
       </c>
       <c r="H51">
         <v>1012</v>
@@ -10671,7 +10671,7 @@
         <v>4.7E-2</v>
       </c>
       <c r="G52">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000003</v>
       </c>
       <c r="H52">
         <v>1188</v>
@@ -10724,7 +10724,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G53">
-        <v>0.21012000000000003</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H53">
         <v>1188</v>
@@ -10777,7 +10777,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="G54">
-        <v>0.21012000000000003</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H54">
         <v>1188</v>
@@ -10830,7 +10830,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G55">
-        <v>0.21011999999999997</v>
+        <v>0.21537299999999995</v>
       </c>
       <c r="H55">
         <v>1188</v>
@@ -10883,7 +10883,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="G56">
-        <v>0.23072000000000004</v>
+        <v>0.236488</v>
       </c>
       <c r="H56">
         <v>1188</v>
@@ -10936,7 +10936,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.21011999999999997</v>
+        <v>0.21537299999999995</v>
       </c>
       <c r="H57">
         <v>1188</v>
@@ -10989,7 +10989,7 @@
         <v>0.03</v>
       </c>
       <c r="G58">
-        <v>0.21012</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H58">
         <v>1188</v>
@@ -11042,7 +11042,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G59">
-        <v>0.21012000000000003</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H59">
         <v>1188</v>
@@ -11095,7 +11095,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G60">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000006</v>
       </c>
       <c r="H60">
         <v>1188</v>
@@ -11148,7 +11148,7 @@
         <v>0.04</v>
       </c>
       <c r="G61">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H61">
         <v>1188</v>
@@ -11201,7 +11201,7 @@
         <v>0.04</v>
       </c>
       <c r="G62">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H62">
         <v>1188</v>
@@ -11254,7 +11254,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G63">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H63">
         <v>1188</v>
@@ -11307,7 +11307,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G64">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H64">
         <v>1188</v>
@@ -11360,7 +11360,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G65">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000006</v>
       </c>
       <c r="H65">
         <v>1188</v>
@@ -11413,7 +11413,7 @@
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="G66">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H66">
         <v>1188</v>
@@ -11466,7 +11466,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G67">
-        <v>0.21011999999999997</v>
+        <v>0.21537300000000001</v>
       </c>
       <c r="H67">
         <v>1188</v>
@@ -11519,7 +11519,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G68">
-        <v>0.21012000000000003</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H68">
         <v>1188</v>
@@ -11572,7 +11572,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G69">
-        <v>0.18128</v>
+        <v>0.18581199999999998</v>
       </c>
       <c r="H69">
         <v>1188</v>
@@ -11625,7 +11625,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G70">
-        <v>0.29252</v>
+        <v>0.29983299999999996</v>
       </c>
       <c r="H70">
         <v>1633.5000000000002</v>
@@ -11678,7 +11678,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G71">
-        <v>0.29252</v>
+        <v>0.29983299999999996</v>
       </c>
       <c r="H71">
         <v>1633.5000000000002</v>
@@ -11731,7 +11731,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G72">
-        <v>0.27192000000000005</v>
+        <v>0.27871800000000002</v>
       </c>
       <c r="H72">
         <v>1782.0000000000002</v>
@@ -11784,7 +11784,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G73">
-        <v>0.27192000000000005</v>
+        <v>0.27871800000000002</v>
       </c>
       <c r="H73">
         <v>1782.0000000000002</v>
@@ -11837,7 +11837,7 @@
         <v>4.36E-2</v>
       </c>
       <c r="G74">
-        <v>0.27192000000000005</v>
+        <v>0.27871800000000002</v>
       </c>
       <c r="H74">
         <v>1782.0000000000002</v>
@@ -11890,7 +11890,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G75">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H75">
         <v>1782.0000000000002</v>
@@ -11943,7 +11943,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G76">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H76">
         <v>1782.0000000000002</v>
@@ -11996,7 +11996,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G77">
-        <v>0.27604000000000001</v>
+        <v>0.282941</v>
       </c>
       <c r="H77">
         <v>1782.0000000000002</v>
@@ -12049,7 +12049,7 @@
         <v>2.7E-2</v>
       </c>
       <c r="G78">
-        <v>0.27604000000000001</v>
+        <v>0.282941</v>
       </c>
       <c r="H78">
         <v>1782.0000000000002</v>
@@ -12102,7 +12102,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G79">
-        <v>0.27192000000000005</v>
+        <v>0.27871800000000002</v>
       </c>
       <c r="H79">
         <v>1518.0000000000002</v>
@@ -12155,7 +12155,7 @@
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="G80">
-        <v>0.26368000000000003</v>
+        <v>0.27027200000000001</v>
       </c>
       <c r="H80">
         <v>1782.0000000000002</v>
@@ -12208,7 +12208,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G81">
-        <v>0.27604000000000001</v>
+        <v>0.282941</v>
       </c>
       <c r="H81">
         <v>1782.0000000000002</v>
@@ -12261,7 +12261,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G82">
-        <v>0.27604000000000001</v>
+        <v>0.282941</v>
       </c>
       <c r="H82">
         <v>1782.0000000000002</v>
@@ -12314,7 +12314,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="G83">
-        <v>0.26368000000000003</v>
+        <v>0.27027200000000001</v>
       </c>
       <c r="H83">
         <v>1782.0000000000002</v>
@@ -12367,7 +12367,7 @@
         <v>4.87E-2</v>
       </c>
       <c r="G84">
-        <v>0.27192000000000005</v>
+        <v>0.27871800000000002</v>
       </c>
       <c r="H84">
         <v>1782.0000000000005</v>
@@ -21430,7 +21430,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="G255">
-        <v>0.39552000000000004</v>
+        <v>0.40540799999999999</v>
       </c>
       <c r="H255">
         <v>1633.5000000000002</v>
@@ -21483,7 +21483,7 @@
         <v>0.2</v>
       </c>
       <c r="G256">
-        <v>0.41200000000000003</v>
+        <v>0.42230000000000006</v>
       </c>
       <c r="H256">
         <v>1391.5</v>
@@ -21536,7 +21536,7 @@
         <v>0.2</v>
       </c>
       <c r="G257">
-        <v>0.41200000000000003</v>
+        <v>0.42230000000000006</v>
       </c>
       <c r="H257">
         <v>1391.5</v>
@@ -21589,7 +21589,7 @@
         <v>0.2</v>
       </c>
       <c r="G258">
-        <v>0.41200000000000003</v>
+        <v>0.42230000000000006</v>
       </c>
       <c r="H258">
         <v>1391.5</v>
@@ -21642,7 +21642,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G259">
-        <v>0.41200000000000003</v>
+        <v>0.42230000000000001</v>
       </c>
       <c r="H259">
         <v>1391.5</v>
@@ -21695,7 +21695,7 @@
         <v>0.125</v>
       </c>
       <c r="G260">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000003</v>
       </c>
       <c r="H260">
         <v>1138.5</v>
@@ -21748,7 +21748,7 @@
         <v>0.125</v>
       </c>
       <c r="G261">
-        <v>0.21012</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H261">
         <v>1138.5</v>
@@ -21801,7 +21801,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G262">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999996</v>
       </c>
       <c r="H262">
         <v>1336.5</v>
@@ -21854,7 +21854,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G263">
-        <v>0.22247999999999998</v>
+        <v>0.22804200000000002</v>
       </c>
       <c r="H263">
         <v>1336.5</v>
@@ -21907,7 +21907,7 @@
         <v>0.05</v>
       </c>
       <c r="G264">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999993</v>
       </c>
       <c r="H264">
         <v>1336.5</v>
@@ -21960,7 +21960,7 @@
         <v>0.04</v>
       </c>
       <c r="G265">
-        <v>0.22248000000000001</v>
+        <v>0.22804199999999999</v>
       </c>
       <c r="H265">
         <v>1336.5</v>
@@ -22013,7 +22013,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G266">
-        <v>0.20188000000000003</v>
+        <v>0.20692699999999997</v>
       </c>
       <c r="H266">
         <v>1336.5</v>
@@ -22066,7 +22066,7 @@
         <v>0.02</v>
       </c>
       <c r="G267">
-        <v>0.20188</v>
+        <v>0.206927</v>
       </c>
       <c r="H267">
         <v>1336.5</v>
@@ -22119,7 +22119,7 @@
         <v>0.02</v>
       </c>
       <c r="G268">
-        <v>0.20188</v>
+        <v>0.206927</v>
       </c>
       <c r="H268">
         <v>1336.5</v>
@@ -22172,7 +22172,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G269">
-        <v>0.19776000000000002</v>
+        <v>0.202704</v>
       </c>
       <c r="H269">
         <v>1138.5</v>
@@ -22225,7 +22225,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G270">
-        <v>0.18128</v>
+        <v>0.18581199999999995</v>
       </c>
       <c r="H270">
         <v>1138.5</v>
@@ -22278,7 +22278,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G271">
-        <v>0.19776000000000002</v>
+        <v>0.202704</v>
       </c>
       <c r="H271">
         <v>1138.5</v>
@@ -22331,7 +22331,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G272">
-        <v>0.21012000000000003</v>
+        <v>0.21537299999999998</v>
       </c>
       <c r="H272">
         <v>1138.5</v>
@@ -22384,7 +22384,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G273">
-        <v>0.18128</v>
+        <v>0.18581199999999995</v>
       </c>
       <c r="H273">
         <v>1138.5</v>
@@ -22437,7 +22437,7 @@
         <v>0.04</v>
       </c>
       <c r="G274">
-        <v>0.22248000000000001</v>
+        <v>0.22804199999999999</v>
       </c>
       <c r="H274">
         <v>1336.5</v>
@@ -22490,7 +22490,7 @@
         <v>0.04</v>
       </c>
       <c r="G275">
-        <v>0.22248000000000001</v>
+        <v>0.22804199999999999</v>
       </c>
       <c r="H275">
         <v>1336.5</v>
@@ -22543,7 +22543,7 @@
         <v>0.13300000000000001</v>
       </c>
       <c r="G276">
-        <v>0.25956000000000001</v>
+        <v>0.26604899999999998</v>
       </c>
       <c r="H276">
         <v>1265</v>
@@ -22596,7 +22596,7 @@
         <v>0.126</v>
       </c>
       <c r="G277">
-        <v>0.28839999999999999</v>
+        <v>0.29560999999999998</v>
       </c>
       <c r="H277">
         <v>1265</v>
@@ -22649,7 +22649,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G278">
-        <v>0.25956000000000001</v>
+        <v>0.26604899999999998</v>
       </c>
       <c r="H278">
         <v>1485.0000000000002</v>
@@ -22702,7 +22702,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G279">
-        <v>0.25544000000000006</v>
+        <v>0.261826</v>
       </c>
       <c r="H279">
         <v>1930.5000000000002</v>
@@ -22755,7 +22755,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="G280">
-        <v>0.25544000000000006</v>
+        <v>0.261826</v>
       </c>
       <c r="H280">
         <v>1930.5000000000002</v>
@@ -22808,7 +22808,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="G281">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999996</v>
       </c>
       <c r="H281">
         <v>1930.5000000000002</v>
@@ -22861,7 +22861,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G282">
-        <v>0.2472</v>
+        <v>0.25337999999999999</v>
       </c>
       <c r="H282">
         <v>1930.5000000000005</v>
@@ -22914,7 +22914,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="G283">
-        <v>0.26780000000000004</v>
+        <v>0.27449500000000004</v>
       </c>
       <c r="H283">
         <v>1930.5000000000007</v>
@@ -22967,7 +22967,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G284">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000003</v>
       </c>
       <c r="H284">
         <v>1930.5000000000007</v>
@@ -23020,7 +23020,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="G285">
-        <v>0.23896000000000001</v>
+        <v>0.24493399999999999</v>
       </c>
       <c r="H285">
         <v>1930.5000000000005</v>
@@ -23073,7 +23073,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="G286">
-        <v>0.23895999999999998</v>
+        <v>0.24493399999999996</v>
       </c>
       <c r="H286">
         <v>1930.5000000000002</v>
@@ -23126,7 +23126,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="G287">
-        <v>0.23072000000000004</v>
+        <v>0.23648800000000003</v>
       </c>
       <c r="H287">
         <v>1930.5000000000007</v>
